--- a/data/trans_orig/Viv_Temp_insuf-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Viv_Temp_insuf-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29683</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23132</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36115</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>26683</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17069</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35037</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>48,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30956</t>
+          <t>23857</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23360</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>53541</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45815</t>
+          <t>43343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67860</t>
+          <t>61570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27049</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20617</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33600</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>27995</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19641</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37609</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>51,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>68,78%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>16430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>28509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>59043</t>
+          <t>49949</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48822</t>
+          <t>41920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70867</t>
+          <t>60147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>194660</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>171781</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>216602</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>40,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>183674</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>149583</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>205610</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>39,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>202524</t>
+          <t>186616</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181632</t>
+          <t>168952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>226575</t>
+          <t>204344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>386198</t>
+          <t>381276</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>341452</t>
+          <t>352589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>414614</t>
+          <t>408330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>281018</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>259076</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>303897</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>59,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>276836</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>254900</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>310927</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>60,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>314095</t>
+          <t>245832</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290044</t>
+          <t>228104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>334987</t>
+          <t>263496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>590931</t>
+          <t>526850</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>562515</t>
+          <t>499796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>635677</t>
+          <t>555537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49392</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>38856</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59503</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>49007</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39822</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59734</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53772</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43027</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66072</t>
+          <t>58818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>102779</t>
+          <t>98257</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88799</t>
+          <t>83967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117165</t>
+          <t>112806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>118070</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>107959</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>128606</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>70,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>76,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>98810</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>88083</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>107995</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>66,85%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128633</t>
+          <t>99319</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116333</t>
+          <t>89367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139378</t>
+          <t>108833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>227443</t>
+          <t>217389</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213057</t>
+          <t>202840</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>241423</t>
+          <t>231679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>147817</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147817</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148185</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148185</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>330222</t>
+          <t>315646</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330222</t>
+          <t>315646</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330222</t>
+          <t>315646</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,107 +1749,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>273735</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>248371</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>297023</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>259364</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>228107</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>285308</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>39,12%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>287252</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263853</t>
+          <t>240325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>314141</t>
+          <t>280673</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>38,31%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>533073</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>501050</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>564825</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>40,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>37,75%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>34,67%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>41,28%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>546616</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>502386</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>580986</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>35,28%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>426137</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>402849</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>451501</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>567</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>403640</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>377696</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>434897</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>60,88%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>473776</t>
+          <t>368052</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>446887</t>
+          <t>346717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>497175</t>
+          <t>387065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>58,66%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>61,69%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>794189</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>762437</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>826212</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>59,84%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>57,44%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>62,25%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>58,72%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>65,33%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1169</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>877416</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>843046</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>921646</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>61,61%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>59,2%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663004</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663004</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663004</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627390</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627390</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627390</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424032</t>
+          <t>1327262</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424032</t>
+          <t>1327262</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424032</t>
+          <t>1327262</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
